--- a/outputs/daily/hr_rankings_2026-09-09.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-09.xlsx
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4466,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5804,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -10844,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12590,34 +12586,30 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14208,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -17008,7 +17000,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -20430,34 +20422,30 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25470,34 +25458,30 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -27714,34 +27698,30 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -29612,7 +29592,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29892,7 +29872,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30172,7 +30152,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -32128,7 +32108,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -32408,7 +32388,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -34648,7 +34628,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -35208,7 +35188,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -36048,7 +36028,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -40524,7 +40504,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -43944,28 +43924,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr"/>
-      <c r="X156" t="inlineStr"/>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y156" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -44778,34 +44762,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44996,7 +44976,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -45276,7 +45256,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -47512,7 +47492,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -48972,28 +48952,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W174" t="inlineStr"/>
-      <c r="X174" t="inlineStr"/>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y174" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49460,7 +49444,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -50364,28 +50348,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W179" t="inlineStr"/>
-      <c r="X179" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y179" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54818,7 +54806,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -55164,34 +55152,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56502,7 +56486,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
